--- a/Draft_2025.xlsx
+++ b/Draft_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Perso\Draft_Algorythm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09204AB9-55F4-4B00-B810-34C583A20949}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA6B41A-69E0-42C0-83F4-A3AF02F3E25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="1" xr2:uid="{4F527041-E097-4BFB-9AF4-3A90D3943DF3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" activeTab="1" xr2:uid="{4F527041-E097-4BFB-9AF4-3A90D3943DF3}"/>
   </bookViews>
   <sheets>
     <sheet name="Roster" sheetId="1" r:id="rId1"/>
